--- a/static/data/exports/Retro_TR_AE_2013.xlsx
+++ b/static/data/exports/Retro_TR_AE_2013.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_AE_2013.xlsx
+++ b/static/data/exports/Retro_TR_AE_2013.xlsx
@@ -540,11 +540,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E2" t="n">
         <v>17063</v>
@@ -850,11 +850,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E7" t="n">
         <v>18368</v>
@@ -1098,11 +1098,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E11" t="n">
         <v>19744</v>
@@ -1408,11 +1408,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E16" t="n">
         <v>17467</v>
@@ -1594,11 +1594,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E19" t="n">
         <v>20972</v>
@@ -1842,11 +1842,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E23" t="n">
         <v>19398</v>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E25" t="n">
         <v>18060</v>
@@ -2834,11 +2834,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E39" t="n">
         <v>21304</v>
@@ -3082,11 +3082,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E43" t="n">
         <v>19275</v>
@@ -3330,11 +3330,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E47" t="n">
         <v>17315</v>
@@ -3578,11 +3578,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E51" t="n">
         <v>23977</v>
@@ -4074,11 +4074,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E59" t="n">
         <v>19808</v>
@@ -4384,11 +4384,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E64" t="n">
         <v>20987</v>
@@ -4694,11 +4694,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E69" t="n">
         <v>19181</v>
@@ -4880,11 +4880,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E72" t="n">
         <v>21613</v>
@@ -5190,11 +5190,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E77" t="n">
         <v>16479</v>
@@ -5376,11 +5376,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E80" t="n">
         <v>17100</v>
@@ -5562,11 +5562,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E83" t="n">
         <v>21969</v>
@@ -5810,11 +5810,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E87" t="n">
         <v>18043</v>
@@ -5934,11 +5934,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E89" t="n">
         <v>21286</v>
@@ -6120,11 +6120,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E92" t="n">
         <v>19504</v>
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E96" t="n">
         <v>22692</v>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E101" t="n">
         <v>17826</v>
@@ -6926,11 +6926,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E105" t="n">
         <v>19755</v>
@@ -7174,11 +7174,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E109" t="n">
         <v>18357</v>
@@ -7484,11 +7484,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E114" t="n">
         <v>17125</v>
@@ -7732,11 +7732,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E118" t="n">
         <v>23600</v>
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E126" t="n">
         <v>22178</v>
@@ -8538,11 +8538,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E131" t="n">
         <v>24947</v>
@@ -8786,11 +8786,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E135" t="n">
         <v>23942</v>
@@ -9034,11 +9034,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E139" t="n">
         <v>20585</v>
@@ -9530,11 +9530,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E147" t="n">
         <v>25009</v>
@@ -9716,11 +9716,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E150" t="n">
         <v>24295</v>
@@ -9840,11 +9840,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E152" t="n">
         <v>21320</v>
@@ -10026,11 +10026,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E155" t="n">
         <v>21404</v>
@@ -10212,11 +10212,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E158" t="n">
         <v>15714</v>
@@ -10522,11 +10522,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E163" t="n">
         <v>19075</v>
@@ -10770,11 +10770,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E167" t="n">
         <v>15526</v>
@@ -11204,11 +11204,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E174" t="n">
         <v>18527</v>
@@ -11452,11 +11452,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E178" t="n">
         <v>19204</v>
@@ -11638,11 +11638,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E181" t="n">
         <v>18648</v>
@@ -12072,11 +12072,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E188" t="n">
         <v>18755</v>
@@ -12444,11 +12444,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E194" t="n">
         <v>14039</v>
@@ -12816,11 +12816,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E200" t="n">
         <v>15870</v>
@@ -13002,11 +13002,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E203" t="n">
         <v>18504</v>
@@ -13312,11 +13312,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E208" t="n">
         <v>17899</v>
@@ -13622,11 +13622,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E213" t="n">
         <v>21009</v>
@@ -13994,11 +13994,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E219" t="n">
         <v>18372</v>
@@ -14242,11 +14242,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E223" t="n">
         <v>14514</v>
@@ -14552,11 +14552,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E228" t="n">
         <v>17991</v>
@@ -14862,11 +14862,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E233" t="n">
         <v>16147</v>
@@ -15172,11 +15172,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E238" t="n">
         <v>18602</v>
@@ -15358,11 +15358,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E241" t="n">
         <v>15196</v>
@@ -15606,11 +15606,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E245" t="n">
         <v>16601</v>
@@ -15792,11 +15792,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E248" t="n">
         <v>17186</v>
